--- a/Timesheet-Project/Timesheet 3/Kayden/Kayden_Padayachee_March_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Kayden/Kayden_Padayachee_March_FinalWeek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Kayden\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kpada\OneDrive - ADvTECH Ltd\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="36" documentId="8_{3AA8B296-F537-4C12-A6EB-80C64274943A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF92E73B-C72F-4672-887E-CBA4656D98B1}"/>
   <bookViews>
-    <workbookView xWindow="2508" yWindow="2508" windowWidth="17280" windowHeight="8880" firstSheet="5" activeTab="5" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Oct" sheetId="10" r:id="rId1"/>
@@ -974,7 +974,7 @@
     <numFmt numFmtId="166" formatCode="_ [$R-1C09]\ * #,##0.00_ ;_ [$R-1C09]\ * \-#,##0.00_ ;_ [$R-1C09]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="[$R-1C09]#,##0.00;\-[$R-1C09]#,##0.00"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2054,28 +2054,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2091,6 +2076,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2149,6 +2149,147 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="103">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2821,147 +2962,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6758C6CA-2356-4535-9D9D-86230C423211}"/>
@@ -3370,23 +3370,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H77" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H77" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="H2:H77" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
   <tableColumns count="1">
-    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="99" dataDxfId="98" tableBorderDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2" tableBorderDxfId="1">
   <autoFilter ref="F2:F40" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:F19">
     <sortCondition ref="F2:F19"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="96"/>
+    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3663,18 +3663,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B63D3D5-6C83-45F2-B2A7-43EE15BF1EF3}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -3695,7 +3695,7 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="37"/>
       <c r="B7" s="46"/>
       <c r="C7" s="37"/>
@@ -3704,7 +3704,7 @@
       <c r="H7" s="40"/>
       <c r="J7" s="41"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="22">
         <v>45931</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="22">
         <v>45932</v>
       </c>
@@ -3788,7 +3788,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="22">
         <v>45933</v>
       </c>
@@ -3807,7 +3807,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="31">
         <v>45934</v>
       </c>
@@ -3826,7 +3826,7 @@
       <c r="I12" s="35"/>
       <c r="J12" s="35"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="31">
         <v>45935</v>
       </c>
@@ -3845,7 +3845,7 @@
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="22">
         <v>45936</v>
       </c>
@@ -3864,7 +3864,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="22">
         <v>45937</v>
       </c>
@@ -3883,7 +3883,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="22">
         <v>45938</v>
       </c>
@@ -3902,7 +3902,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="22">
         <v>45939</v>
       </c>
@@ -3921,7 +3921,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="22">
         <v>45940</v>
       </c>
@@ -3940,7 +3940,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="31">
         <v>45941</v>
       </c>
@@ -3959,7 +3959,7 @@
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="31">
         <v>45942</v>
       </c>
@@ -3978,7 +3978,7 @@
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="22">
         <v>45943</v>
       </c>
@@ -3997,7 +3997,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="22">
         <v>45944</v>
       </c>
@@ -4016,7 +4016,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="22">
         <v>45945</v>
       </c>
@@ -4035,7 +4035,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="22">
         <v>45946</v>
       </c>
@@ -4054,7 +4054,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>45947</v>
       </c>
@@ -4073,7 +4073,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="31">
         <v>45948</v>
       </c>
@@ -4092,7 +4092,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="31">
         <v>45949</v>
       </c>
@@ -4111,7 +4111,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="22">
         <v>45950</v>
       </c>
@@ -4130,7 +4130,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="22">
         <v>45951</v>
       </c>
@@ -4149,7 +4149,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="22">
         <v>45952</v>
       </c>
@@ -4168,7 +4168,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="22">
         <v>45953</v>
       </c>
@@ -4187,7 +4187,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="22">
         <v>45954</v>
       </c>
@@ -4206,7 +4206,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="31">
         <v>45955</v>
       </c>
@@ -4225,7 +4225,7 @@
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="31">
         <v>45956</v>
       </c>
@@ -4244,7 +4244,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="22">
         <v>45957</v>
       </c>
@@ -4263,7 +4263,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="22">
         <v>45958</v>
       </c>
@@ -4282,7 +4282,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="22">
         <v>45959</v>
       </c>
@@ -4301,7 +4301,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="22">
         <v>45960</v>
       </c>
@@ -4320,7 +4320,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="13.9" customHeight="1">
       <c r="A39" s="22">
         <v>45961</v>
       </c>
@@ -4339,7 +4339,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A40" s="46"/>
       <c r="B40" s="46"/>
       <c r="G40" s="40"/>
@@ -4347,7 +4347,7 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
     </row>
-    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="13.9" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A43" s="116" t="s">
         <v>27</v>
       </c>
@@ -4385,7 +4385,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="13.9">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A45" s="117" t="s">
         <v>29</v>
       </c>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="14.45" thickBot="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.9" thickBot="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4438,7 +4438,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="13.9" thickBot="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4449,7 +4449,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:8" ht="13.15" thickBot="1">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -4460,56 +4460,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D7:E7">
-    <cfRule type="containsText" dxfId="95" priority="12" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="102" priority="12" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="13" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="101" priority="13" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="93" priority="14" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="100" priority="14" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="15" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="99" priority="15" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="16" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="98" priority="16" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="17" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="97" priority="17" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="18" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B49">
-    <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="95" priority="1" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="87" priority="2" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="94" priority="2" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="86" priority="3" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="93" priority="3" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="4" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="92" priority="4" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="5" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="91" priority="5" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="6" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="90" priority="6" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="7" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="89" priority="7" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="8" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="88" priority="8" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="9" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4557,18 +4557,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE93A-CBFB-4D27-9D4A-1E2332DAE6F0}">
   <dimension ref="A5:J48"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -4578,7 +4578,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -4592,10 +4592,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="31">
         <v>45962</v>
       </c>
@@ -4646,7 +4646,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="31">
         <v>45963</v>
       </c>
@@ -4665,7 +4665,7 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="22">
         <v>45964</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="22">
         <v>45965</v>
       </c>
@@ -4717,7 +4717,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="22">
         <v>45966</v>
       </c>
@@ -4736,7 +4736,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="22">
         <v>45967</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="22">
         <v>45968</v>
       </c>
@@ -4774,7 +4774,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="31">
         <v>45969</v>
       </c>
@@ -4793,7 +4793,7 @@
       <c r="I16" s="35"/>
       <c r="J16" s="35"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="31">
         <v>45970</v>
       </c>
@@ -4812,7 +4812,7 @@
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="22">
         <v>45971</v>
       </c>
@@ -4831,7 +4831,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="22">
         <v>45972</v>
       </c>
@@ -4850,7 +4850,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="22">
         <v>45973</v>
       </c>
@@ -4869,7 +4869,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="22">
         <v>45974</v>
       </c>
@@ -4888,7 +4888,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="22">
         <v>45975</v>
       </c>
@@ -4907,7 +4907,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="31">
         <v>45976</v>
       </c>
@@ -4926,7 +4926,7 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="31">
         <v>45977</v>
       </c>
@@ -4945,7 +4945,7 @@
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>45978</v>
       </c>
@@ -4964,7 +4964,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="22">
         <v>45979</v>
       </c>
@@ -4983,7 +4983,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="22">
         <v>45980</v>
       </c>
@@ -5002,7 +5002,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="22">
         <v>45981</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="22">
         <v>45982</v>
       </c>
@@ -5040,7 +5040,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="31">
         <v>45983</v>
       </c>
@@ -5059,7 +5059,7 @@
       <c r="I30" s="35"/>
       <c r="J30" s="35"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="31">
         <v>45984</v>
       </c>
@@ -5078,7 +5078,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="22">
         <v>45985</v>
       </c>
@@ -5097,7 +5097,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="22">
         <v>45986</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="22">
         <v>45987</v>
       </c>
@@ -5135,7 +5135,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="22">
         <v>45988</v>
       </c>
@@ -5154,7 +5154,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="22">
         <v>45989</v>
       </c>
@@ -5173,7 +5173,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="31">
         <v>45990</v>
       </c>
@@ -5192,7 +5192,7 @@
       <c r="I37" s="35"/>
       <c r="J37" s="35"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="31">
         <v>45991</v>
       </c>
@@ -5211,7 +5211,7 @@
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
     </row>
-    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A39" s="46"/>
       <c r="B39" s="45"/>
       <c r="C39" s="45"/>
@@ -5222,7 +5222,7 @@
       <c r="H39" s="36"/>
       <c r="I39" s="37"/>
     </row>
-    <row r="40" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="13.9" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="9"/>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="116" t="s">
         <v>27</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="F42" s="2"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="13.9">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A44" s="117" t="s">
         <v>29</v>
       </c>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="14.45" thickBot="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="13.9" thickBot="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -5313,7 +5313,7 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.9" thickBot="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5324,7 +5324,7 @@
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="13.15" thickBot="1">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -5335,56 +5335,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="79" priority="21" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="86" priority="21" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="22" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="85" priority="22" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="23" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="24" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="83" priority="24" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="25" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="82" priority="25" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="26" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="81" priority="26" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="27" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B48">
-    <cfRule type="containsText" dxfId="72" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="79" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="71" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="78" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:E40 D42:E44 E47">
-    <cfRule type="containsText" dxfId="70" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="77" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="76" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="75" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="74" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="73" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="72" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5436,18 +5436,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738C92ED-F226-4107-8C14-FCA383B998C3}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -5457,7 +5457,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -5471,10 +5471,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="22">
         <v>45992</v>
       </c>
@@ -5539,7 +5539,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="22">
         <v>45993</v>
       </c>
@@ -5558,7 +5558,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="22">
         <v>45994</v>
       </c>
@@ -5577,7 +5577,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="22">
         <v>45995</v>
       </c>
@@ -5596,7 +5596,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="22">
         <v>45996</v>
       </c>
@@ -5615,7 +5615,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="31">
         <v>45997</v>
       </c>
@@ -5634,7 +5634,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="31">
         <v>45998</v>
       </c>
@@ -5653,7 +5653,7 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="22">
         <v>45999</v>
       </c>
@@ -5672,7 +5672,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="22">
         <v>46000</v>
       </c>
@@ -5691,7 +5691,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="22">
         <v>46001</v>
       </c>
@@ -5710,7 +5710,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="22">
         <v>46002</v>
       </c>
@@ -5729,7 +5729,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="22">
         <v>46003</v>
       </c>
@@ -5748,7 +5748,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="31">
         <v>46004</v>
       </c>
@@ -5767,7 +5767,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="31">
         <v>46005</v>
       </c>
@@ -5786,7 +5786,7 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="22">
         <v>46006</v>
       </c>
@@ -5805,7 +5805,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="47">
         <v>46007</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>46008</v>
       </c>
@@ -5855,7 +5855,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="22">
         <v>46009</v>
       </c>
@@ -5874,7 +5874,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="22">
         <v>46010</v>
       </c>
@@ -5893,7 +5893,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="31">
         <v>46011</v>
       </c>
@@ -5912,7 +5912,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="31">
         <v>46012</v>
       </c>
@@ -5931,7 +5931,7 @@
       <c r="I29" s="35"/>
       <c r="J29" s="35"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="22">
         <v>46013</v>
       </c>
@@ -5950,7 +5950,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="22">
         <v>46014</v>
       </c>
@@ -5969,7 +5969,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="22">
         <v>46015</v>
       </c>
@@ -5988,7 +5988,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="47">
         <v>46016</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="47">
         <v>46017</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="31">
         <v>46018</v>
       </c>
@@ -6069,7 +6069,7 @@
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="31">
         <v>46019</v>
       </c>
@@ -6088,7 +6088,7 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="22">
         <v>46020</v>
       </c>
@@ -6107,7 +6107,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="22">
         <v>46021</v>
       </c>
@@ -6126,7 +6126,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A39" s="22">
         <v>46022</v>
       </c>
@@ -6145,7 +6145,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A40" s="45"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -6156,7 +6156,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="13.9" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A43" s="116" t="s">
         <v>27</v>
       </c>
@@ -6194,7 +6194,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="13.9">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A45" s="117" t="s">
         <v>29</v>
       </c>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="14.45" thickBot="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.9" thickBot="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6247,7 +6247,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="13.9" thickBot="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -6258,7 +6258,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:8" ht="13.15" thickBot="1">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -6269,56 +6269,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="63" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="70" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="69" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="68" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="67" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="66" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="56" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="63" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="62" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="60" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="59" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="58" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6370,18 +6370,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077AC14-6A48-4DDF-A891-D5BFFE7E5F3C}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -6391,7 +6391,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -6405,10 +6405,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="47">
         <v>46023</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="22">
         <v>46024</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="31">
         <v>46025</v>
       </c>
@@ -6525,7 +6525,7 @@
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="31">
         <v>46026</v>
       </c>
@@ -6544,7 +6544,7 @@
       <c r="I12" s="35"/>
       <c r="J12" s="35"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="22">
         <v>46027</v>
       </c>
@@ -6563,7 +6563,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="22">
         <v>46028</v>
       </c>
@@ -6582,7 +6582,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="22">
         <v>46029</v>
       </c>
@@ -6601,7 +6601,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="22">
         <v>46030</v>
       </c>
@@ -6620,7 +6620,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="22">
         <v>46031</v>
       </c>
@@ -6639,7 +6639,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="31">
         <v>46032</v>
       </c>
@@ -6658,7 +6658,7 @@
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="31">
         <v>46033</v>
       </c>
@@ -6677,7 +6677,7 @@
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="22">
         <v>46034</v>
       </c>
@@ -6696,7 +6696,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="22">
         <v>46035</v>
       </c>
@@ -6715,7 +6715,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="22">
         <v>46036</v>
       </c>
@@ -6734,7 +6734,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="22">
         <v>46037</v>
       </c>
@@ -6753,7 +6753,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="22">
         <v>46038</v>
       </c>
@@ -6772,7 +6772,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="31">
         <v>46039</v>
       </c>
@@ -6791,7 +6791,7 @@
       <c r="I25" s="35"/>
       <c r="J25" s="35"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="31">
         <v>46040</v>
       </c>
@@ -6810,7 +6810,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="22">
         <v>46041</v>
       </c>
@@ -6829,7 +6829,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="22">
         <v>46042</v>
       </c>
@@ -6848,7 +6848,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="22">
         <v>46043</v>
       </c>
@@ -6867,7 +6867,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="22">
         <v>46044</v>
       </c>
@@ -6886,7 +6886,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="22">
         <v>46045</v>
       </c>
@@ -6905,7 +6905,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="31">
         <v>46046</v>
       </c>
@@ -6924,7 +6924,7 @@
       <c r="I32" s="35"/>
       <c r="J32" s="35"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="31">
         <v>46047</v>
       </c>
@@ -6943,7 +6943,7 @@
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="22">
         <v>46048</v>
       </c>
@@ -6962,7 +6962,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="22">
         <v>46049</v>
       </c>
@@ -6981,7 +6981,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="22">
         <v>46050</v>
       </c>
@@ -7000,7 +7000,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="22">
         <v>46051</v>
       </c>
@@ -7019,7 +7019,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="22">
         <v>46052</v>
       </c>
@@ -7038,7 +7038,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="13.15" thickBot="1">
       <c r="A39" s="31">
         <v>46053</v>
       </c>
@@ -7057,7 +7057,7 @@
       <c r="I39" s="35"/>
       <c r="J39" s="35"/>
     </row>
-    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -7068,7 +7068,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="13.9" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A43" s="116" t="s">
         <v>27</v>
       </c>
@@ -7106,7 +7106,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="13.9">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A45" s="117" t="s">
         <v>29</v>
       </c>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="14.45" thickBot="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.9" thickBot="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -7159,7 +7159,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="13.9" thickBot="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -7170,7 +7170,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:8" ht="13.15" thickBot="1">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -7181,56 +7181,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="47" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="54" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="53" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="52" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="51" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="50" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="49" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="47" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="46" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="44" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="42" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="40" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7298,18 +7298,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5FF808-4CDC-4429-9978-CAD26FE6591A}">
   <dimension ref="A5:J46"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -7319,7 +7319,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -7333,10 +7333,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="31">
         <v>46054</v>
       </c>
@@ -7387,7 +7387,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="22">
         <v>46055</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="22">
         <v>46056</v>
       </c>
@@ -7433,7 +7433,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="22">
         <v>46057</v>
       </c>
@@ -7452,7 +7452,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="22">
         <v>46058</v>
       </c>
@@ -7471,7 +7471,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="22">
         <v>46059</v>
       </c>
@@ -7490,7 +7490,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="31">
         <v>46060</v>
       </c>
@@ -7509,7 +7509,7 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="31">
         <v>46061</v>
       </c>
@@ -7528,7 +7528,7 @@
       <c r="I16" s="35"/>
       <c r="J16" s="35"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="22">
         <v>46062</v>
       </c>
@@ -7544,7 +7544,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="22">
         <v>46063</v>
       </c>
@@ -7563,7 +7563,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="22">
         <v>46064</v>
       </c>
@@ -7582,7 +7582,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="22">
         <v>46065</v>
       </c>
@@ -7601,7 +7601,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="22">
         <v>46066</v>
       </c>
@@ -7620,7 +7620,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="31">
         <v>46067</v>
       </c>
@@ -7639,7 +7639,7 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="31">
         <v>46068</v>
       </c>
@@ -7658,7 +7658,7 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="22">
         <v>46069</v>
       </c>
@@ -7677,7 +7677,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>46070</v>
       </c>
@@ -7696,7 +7696,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="22">
         <v>46071</v>
       </c>
@@ -7715,7 +7715,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="22">
         <v>46072</v>
       </c>
@@ -7734,7 +7734,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="22">
         <v>46073</v>
       </c>
@@ -7753,7 +7753,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="31">
         <v>46074</v>
       </c>
@@ -7772,7 +7772,7 @@
       <c r="I29" s="35"/>
       <c r="J29" s="35"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="31">
         <v>46075</v>
       </c>
@@ -7791,7 +7791,7 @@
       <c r="I30" s="35"/>
       <c r="J30" s="35"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="22">
         <v>46076</v>
       </c>
@@ -7810,7 +7810,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="22">
         <v>46077</v>
       </c>
@@ -7829,7 +7829,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="22">
         <v>46078</v>
       </c>
@@ -7848,7 +7848,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="22">
         <v>46079</v>
       </c>
@@ -7867,7 +7867,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="22">
         <v>46080</v>
       </c>
@@ -7886,7 +7886,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="13.9" customHeight="1">
       <c r="A36" s="31">
         <v>46081</v>
       </c>
@@ -7905,7 +7905,7 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
     </row>
-    <row r="37" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A37" s="46"/>
       <c r="B37" s="45"/>
       <c r="C37" s="45"/>
@@ -7916,7 +7916,7 @@
       <c r="H37" s="36"/>
       <c r="I37" s="37"/>
     </row>
-    <row r="38" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="13.9" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H38" s="40"/>
     </row>
-    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="9"/>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="H39" s="40"/>
     </row>
-    <row r="40" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="14.45" thickBot="1">
       <c r="A40" s="116" t="s">
         <v>27</v>
       </c>
@@ -7954,7 +7954,7 @@
       <c r="F40" s="2"/>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="15" customHeight="1">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="6"/>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="H41" s="38"/>
     </row>
-    <row r="42" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="14.45" thickBot="1">
       <c r="A42" s="117" t="s">
         <v>29</v>
       </c>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="14.45" thickBot="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="13.9" thickBot="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -8007,7 +8007,7 @@
       <c r="F44" s="2"/>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="13.9" thickBot="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -8018,7 +8018,7 @@
       <c r="F45" s="21"/>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="13.15" thickBot="1">
       <c r="E46" s="39"/>
       <c r="H46" s="40"/>
     </row>
@@ -8029,56 +8029,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="31" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="38" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="37" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="36" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="35" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="33" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B46">
-    <cfRule type="containsText" dxfId="24" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37:E38 D40:E42 E45">
-    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8130,18 +8130,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1366D5-46F5-410C-BC9F-D56DCF566D28}">
   <dimension ref="A5:J73"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.6">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -8151,7 +8151,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="12.6">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -8165,10 +8165,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="12.6">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="31">
         <v>46082</v>
       </c>
@@ -8219,7 +8219,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="22">
         <v>46083</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="25.5">
       <c r="A11" s="22">
         <v>46083</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>0.94305555555555554</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="63">
       <c r="A12" s="22">
         <v>46084</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="25.5">
       <c r="A13" s="22">
         <v>46085</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>0.50347222222222221</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="50.25">
       <c r="A14" s="22">
         <v>46085</v>
       </c>
@@ -8373,7 +8373,7 @@
         <v>0.63541666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="22">
         <v>46085</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="25.5">
       <c r="A16" s="22">
         <v>46086</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>0.50208333333333333</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="37.5">
       <c r="A17" s="22">
         <v>46086</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>0.73819444444444449</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="63">
       <c r="A18" s="22">
         <v>46087</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>0.50069444444444444</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="25.5">
       <c r="A19" s="22">
         <v>46087</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>0.73402777777777772</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="31">
         <v>46088</v>
       </c>
@@ -8541,13 +8541,13 @@
       <c r="F20" s="32"/>
       <c r="G20" s="33"/>
       <c r="H20" s="34">
-        <f t="shared" ref="H20:H35" si="1">J20-I20</f>
+        <f t="shared" ref="H10:H35" si="1">J20-I20</f>
         <v>0</v>
       </c>
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="31">
         <v>46089</v>
       </c>
@@ -8566,7 +8566,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10" ht="100.8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="100.5">
       <c r="A22" s="22">
         <v>46090</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="25.5">
       <c r="A23" s="22">
         <v>46090</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="88.5">
       <c r="A24" s="22">
         <v>46090</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>0.7104166666666667</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="63">
       <c r="A25" s="22">
         <v>46091</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>0.5083333333333333</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="50.25">
       <c r="A26" s="22">
         <v>46091</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>0.72569444444444442</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="63">
       <c r="A27" s="22">
         <v>46092</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>0.52569444444444446</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="37.5">
       <c r="A28" s="22">
         <v>46092</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="75.75">
       <c r="A29" s="22">
         <v>46093</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>0.51597222222222228</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="37.5">
       <c r="A30" s="22">
         <v>46093</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>0.73541666666666672</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="88.5">
       <c r="A31" s="22">
         <v>46094</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>0.52013888888888893</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="50.25">
       <c r="A32" s="22">
         <v>46094</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>0.71250000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="31">
         <v>46095</v>
       </c>
@@ -8925,7 +8925,7 @@
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="31">
         <v>46096</v>
       </c>
@@ -8944,7 +8944,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="75.75">
       <c r="A35" s="22">
         <v>46097</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>0.52638888888888891</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="50.25">
       <c r="A36" s="22">
         <v>46097</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>0.71597222222222223</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="63">
       <c r="A37" s="22">
         <v>46098</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>67</v>
       </c>
       <c r="H37" s="29">
-        <f t="shared" ref="H37:H44" si="2">J37-I37</f>
+        <f>J37-I37</f>
         <v>0.19513888888888892</v>
       </c>
       <c r="I37" s="30">
@@ -9036,7 +9036,7 @@
         <v>0.52847222222222223</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="50.25">
       <c r="A38" s="22">
         <v>46098</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>68</v>
       </c>
       <c r="H38" s="29">
-        <f t="shared" si="2"/>
+        <f>J38-I38</f>
         <v>0.18819444444444444</v>
       </c>
       <c r="I38" s="30">
@@ -9067,7 +9067,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="75.75">
       <c r="A39" s="22">
         <v>46099</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>69</v>
       </c>
       <c r="H39" s="29">
-        <f t="shared" si="2"/>
+        <f>J39-I39</f>
         <v>0.19513888888888892</v>
       </c>
       <c r="I39" s="30">
@@ -9098,7 +9098,7 @@
         <v>0.52847222222222223</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="50.25">
       <c r="A40" s="22">
         <v>46099</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>70</v>
       </c>
       <c r="H40" s="29">
-        <f t="shared" si="2"/>
+        <f>J40-I40</f>
         <v>0.14861111111111114</v>
       </c>
       <c r="I40" s="30">
@@ -9129,7 +9129,7 @@
         <v>0.71805555555555556</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="63">
       <c r="A41" s="22">
         <v>46100</v>
       </c>
@@ -9150,7 +9150,7 @@
         <v>71</v>
       </c>
       <c r="H41" s="29">
-        <f t="shared" si="2"/>
+        <f>J41-I41</f>
         <v>0.18750000000000006</v>
       </c>
       <c r="I41" s="30">
@@ -9160,7 +9160,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="63">
       <c r="A42" s="22">
         <v>46100</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>72</v>
       </c>
       <c r="H42" s="29">
-        <f t="shared" si="2"/>
+        <f>J42-I42</f>
         <v>0.1479166666666667</v>
       </c>
       <c r="I42" s="30">
@@ -9191,7 +9191,7 @@
         <v>0.70902777777777781</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="63">
       <c r="A43" s="22">
         <v>46101</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>73</v>
       </c>
       <c r="H43" s="29">
-        <f t="shared" si="2"/>
+        <f>J43-I43</f>
         <v>0.16597222222222224</v>
       </c>
       <c r="I43" s="30">
@@ -9222,7 +9222,7 @@
         <v>0.49930555555555556</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="113.4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="88.5">
       <c r="A44" s="22">
         <v>46101</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>74</v>
       </c>
       <c r="H44" s="29">
-        <f t="shared" si="2"/>
+        <f>J44-I44</f>
         <v>0.1743055555555556</v>
       </c>
       <c r="I44" s="30">
@@ -9253,7 +9253,7 @@
         <v>0.71180555555555558</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10">
       <c r="A45" s="31">
         <v>46102</v>
       </c>
@@ -9274,7 +9274,7 @@
         <v>75</v>
       </c>
       <c r="H45" s="50">
-        <f t="shared" ref="H45:H63" si="3">J45-I45</f>
+        <f t="shared" ref="H45:H63" si="2">J45-I45</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="I45" s="51">
@@ -9284,7 +9284,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="A46" s="31">
         <v>46103</v>
       </c>
@@ -9297,13 +9297,13 @@
       <c r="F46" s="32"/>
       <c r="G46" s="33"/>
       <c r="H46" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I46" s="35"/>
       <c r="J46" s="35"/>
     </row>
-    <row r="47" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="37.5">
       <c r="A47" s="22">
         <v>46104</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>76</v>
       </c>
       <c r="H47" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.19791666666666669</v>
       </c>
       <c r="I47" s="30">
@@ -9334,7 +9334,7 @@
         <v>0.53125</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="50.25">
       <c r="A48" s="22">
         <v>46104</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="37.5">
       <c r="A49" s="22">
         <v>46105</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>78</v>
       </c>
       <c r="H49" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.19444444444444448</v>
       </c>
       <c r="I49" s="30">
@@ -9395,7 +9395,7 @@
         <v>0.52777777777777779</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="37.5">
       <c r="A50" s="22">
         <v>46105</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>79</v>
       </c>
       <c r="H50" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.1479166666666667</v>
       </c>
       <c r="I50" s="30">
@@ -9426,7 +9426,7 @@
         <v>0.71527777777777779</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="25.5">
       <c r="A51" s="22">
         <v>46106</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>80</v>
       </c>
       <c r="H51" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>8.4027777777777812E-2</v>
       </c>
       <c r="I51" s="30">
@@ -9457,7 +9457,7 @@
         <v>0.41736111111111113</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="25.5">
       <c r="A52" s="22">
         <v>46106</v>
       </c>
@@ -9478,7 +9478,7 @@
         <v>81</v>
       </c>
       <c r="H52" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>8.8194444444444409E-2</v>
       </c>
       <c r="I52" s="30">
@@ -9488,7 +9488,7 @@
         <v>0.51249999999999996</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="63">
       <c r="A53" s="22">
         <v>46106</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>82</v>
       </c>
       <c r="H53" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.25138888888888888</v>
       </c>
       <c r="I53" s="30">
@@ -9519,7 +9519,7 @@
         <v>0.7993055555555556</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="13.9" customHeight="1">
       <c r="A54" s="22">
         <v>46107</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>83</v>
       </c>
       <c r="H54" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.19444444444444448</v>
       </c>
       <c r="I54" s="30">
@@ -9550,7 +9550,7 @@
         <v>0.52777777777777779</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="13.9" customHeight="1">
       <c r="A55" s="22">
         <v>46107</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>84</v>
       </c>
       <c r="H55" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.15625</v>
       </c>
       <c r="I55" s="30">
@@ -9581,7 +9581,7 @@
         <v>0.72222222222222221</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="13.9" customHeight="1">
       <c r="A56" s="22">
         <v>46108</v>
       </c>
@@ -9602,7 +9602,7 @@
         <v>85</v>
       </c>
       <c r="H56" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.19722222222222224</v>
       </c>
       <c r="I56" s="30">
@@ -9612,7 +9612,7 @@
         <v>0.53055555555555556</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="13.9" customHeight="1">
       <c r="A57" s="22">
         <v>46108</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>86</v>
       </c>
       <c r="H57" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.13888888888888895</v>
       </c>
       <c r="I57" s="30">
@@ -9643,7 +9643,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="13.9" customHeight="1">
       <c r="A58" s="31">
         <v>46109</v>
       </c>
@@ -9656,13 +9656,13 @@
       <c r="F58" s="32"/>
       <c r="G58" s="33"/>
       <c r="H58" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I58" s="35"/>
       <c r="J58" s="35"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10">
       <c r="A59" s="31">
         <v>46110</v>
       </c>
@@ -9675,13 +9675,13 @@
       <c r="F59" s="32"/>
       <c r="G59" s="33"/>
       <c r="H59" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I59" s="35"/>
       <c r="J59" s="35"/>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="15" customHeight="1">
       <c r="A60" s="22">
         <v>46111</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>87</v>
       </c>
       <c r="H60" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.18750000000000006</v>
       </c>
       <c r="I60" s="30">
@@ -9712,7 +9712,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="25.5">
       <c r="A61" s="22">
         <v>46111</v>
       </c>
@@ -9743,7 +9743,7 @@
         <v>0.71180555555555558</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="37.5">
       <c r="A62" s="22">
         <v>46112</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>0.51249999999999996</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="25.5">
       <c r="A63" s="22">
         <v>46112</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>90</v>
       </c>
       <c r="H63" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.17361111111111105</v>
       </c>
       <c r="I63" s="30">
@@ -9805,7 +9805,7 @@
         <v>0.72569444444444442</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10">
       <c r="A64" s="46"/>
       <c r="B64" s="46"/>
       <c r="C64" s="45"/>
@@ -9816,7 +9816,7 @@
       <c r="H64" s="36"/>
       <c r="I64" s="37"/>
     </row>
-    <row r="65" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="H65" s="40"/>
     </row>
-    <row r="66" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="9"/>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="H66" s="40"/>
     </row>
-    <row r="67" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="14.25">
       <c r="A67" s="116" t="s">
         <v>27</v>
       </c>
@@ -9854,7 +9854,7 @@
       <c r="F67" s="2"/>
       <c r="H67" s="40"/>
     </row>
-    <row r="68" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="14.25">
       <c r="A68" s="13"/>
       <c r="B68" s="13"/>
       <c r="C68" s="6"/>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="H68" s="38"/>
     </row>
-    <row r="69" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="14.25">
       <c r="A69" s="117" t="s">
         <v>29</v>
       </c>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="H69" s="40"/>
     </row>
-    <row r="70" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="14.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="H70" s="40"/>
     </row>
-    <row r="71" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -9907,7 +9907,7 @@
       <c r="F71" s="2"/>
       <c r="H71" s="40"/>
     </row>
-    <row r="72" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -9918,7 +9918,7 @@
       <c r="F72" s="21"/>
       <c r="H72" s="40"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8">
       <c r="E73" s="39"/>
       <c r="H73" s="40"/>
     </row>
@@ -9929,56 +9929,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7 D64:E65">
-    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="22" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B73">
-    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:E69 E72">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D67)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D67)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D67)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D67)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D67)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D67)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10034,18 +10034,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368E8809-782A-4EC8-A7EE-23E6EB29126F}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69921875" style="23"/>
-    <col min="5" max="5" width="13.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="23"/>
+    <col min="5" max="5" width="13.25" style="23" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="23" customWidth="1"/>
-    <col min="7" max="16384" width="8.69921875" style="23"/>
+    <col min="7" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="13.5" customHeight="1">
       <c r="A1" s="81"/>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
@@ -10053,7 +10053,7 @@
       <c r="E1" s="81"/>
       <c r="F1" s="81"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2" s="80"/>
       <c r="B2" s="80"/>
       <c r="C2" s="85"/>
@@ -10061,7 +10061,7 @@
       <c r="E2" s="85"/>
       <c r="F2" s="85"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="86"/>
@@ -10069,7 +10069,7 @@
       <c r="E3" s="86"/>
       <c r="F3" s="86"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="87"/>
@@ -10077,7 +10077,7 @@
       <c r="E4" s="87"/>
       <c r="F4" s="87"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -10089,7 +10089,7 @@
       <c r="E5" s="87"/>
       <c r="F5" s="87"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="A6" s="80" t="s">
         <v>91</v>
       </c>
@@ -10102,7 +10102,7 @@
       <c r="E6" s="86"/>
       <c r="F6" s="86"/>
     </row>
-    <row r="7" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="13.5" customHeight="1">
       <c r="A7" s="74"/>
       <c r="B7" s="75"/>
       <c r="C7" s="75"/>
@@ -10110,125 +10110,125 @@
       <c r="E7" s="86"/>
       <c r="F7" s="86"/>
     </row>
-    <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="123" t="s">
+    <row r="8" spans="1:15" ht="27.4" customHeight="1">
+      <c r="A8" s="126" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="123"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
-    </row>
-    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="126"/>
+    </row>
+    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1">
       <c r="A9" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="120" t="s">
+      <c r="C9" s="130"/>
+      <c r="D9" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="121"/>
+      <c r="E9" s="130"/>
       <c r="F9" s="84" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15">
       <c r="A10" s="79"/>
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="120" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122" t="s">
+      <c r="C10" s="120"/>
+      <c r="D10" s="120" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="122"/>
+      <c r="E10" s="120"/>
       <c r="F10" s="78">
         <v>200</v>
       </c>
-      <c r="G10" s="118" t="s">
+      <c r="G10" s="127" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="119"/>
-      <c r="N10" s="119"/>
-      <c r="O10" s="119"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="79"/>
-      <c r="B11" s="124" t="s">
+      <c r="B11" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="125"/>
-      <c r="D11" s="122" t="s">
+      <c r="C11" s="119"/>
+      <c r="D11" s="120" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="122"/>
+      <c r="E11" s="120"/>
       <c r="F11" s="78"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15">
       <c r="A12" s="79"/>
-      <c r="B12" s="124" t="s">
+      <c r="B12" s="118" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="120"/>
       <c r="F12" s="78"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15">
       <c r="A13" s="79"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="120"/>
       <c r="F13" s="78"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15">
       <c r="A14" s="79"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
       <c r="F14" s="78"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15">
       <c r="A15" s="79"/>
-      <c r="B15" s="129"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="120"/>
       <c r="F15" s="78"/>
     </row>
-    <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="13.15" thickBot="1">
       <c r="A16" s="79"/>
-      <c r="B16" s="124"/>
-      <c r="C16" s="125"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
       <c r="F16" s="78"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="126" t="s">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A17" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="127"/>
-      <c r="C17" s="127"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="128"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="123"/>
       <c r="F17" s="77">
         <f>SUM(F10:F16)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="74"/>
       <c r="B18" s="75"/>
       <c r="C18" s="75"/>
@@ -10238,6 +10238,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -10247,16 +10257,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -10286,19 +10286,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0517D5F3-AC91-43ED-96BB-0299CBED5EE0}">
   <dimension ref="A4:F23"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="15.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" style="23" customWidth="1"/>
-    <col min="3" max="3" width="9.69921875" style="23" customWidth="1"/>
-    <col min="4" max="16384" width="8.69921875" style="23"/>
+    <col min="2" max="2" width="11.75" style="23" customWidth="1"/>
+    <col min="3" max="3" width="9.75" style="23" customWidth="1"/>
+    <col min="4" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="131"/>
       <c r="B4" s="131"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -10306,23 +10306,23 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="80" t="s">
         <v>104</v>
       </c>
       <c r="B6" s="80"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="96" t="s">
         <v>105</v>
       </c>
       <c r="B7" s="96"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="97"/>
       <c r="B8" s="86"/>
     </row>
-    <row r="9" spans="1:6" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="27.4" customHeight="1">
       <c r="A9" s="144" t="s">
         <v>106</v>
       </c>
@@ -10332,7 +10332,7 @@
       <c r="E9" s="144"/>
       <c r="F9" s="144"/>
     </row>
-    <row r="10" spans="1:6" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="25.15">
       <c r="A10" s="88" t="s">
         <v>107</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="88"/>
       <c r="B11" s="88"/>
       <c r="C11" s="88"/>
@@ -10360,7 +10360,7 @@
       <c r="E11" s="88"/>
       <c r="F11" s="88"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="88"/>
       <c r="B12" s="88"/>
       <c r="C12" s="88"/>
@@ -10368,7 +10368,7 @@
       <c r="E12" s="88"/>
       <c r="F12" s="88"/>
     </row>
-    <row r="13" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.15" thickBot="1">
       <c r="A13" s="88"/>
       <c r="B13" s="88"/>
       <c r="C13" s="88"/>
@@ -10376,7 +10376,7 @@
       <c r="E13" s="88"/>
       <c r="F13" s="88"/>
     </row>
-    <row r="14" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.15" thickBot="1">
       <c r="A14" s="89"/>
       <c r="B14" s="90"/>
       <c r="C14" s="90"/>
@@ -10387,7 +10387,7 @@
       <c r="E14" s="90"/>
       <c r="F14" s="92"/>
     </row>
-    <row r="15" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.15" thickBot="1">
       <c r="A15" s="135"/>
       <c r="B15" s="136"/>
       <c r="C15" s="136"/>
@@ -10395,7 +10395,7 @@
       <c r="E15" s="136"/>
       <c r="F15" s="136"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="145" t="s">
         <v>113</v>
       </c>
@@ -10405,7 +10405,7 @@
       <c r="E16" s="146"/>
       <c r="F16" s="147"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="132"/>
       <c r="B17" s="133"/>
       <c r="C17" s="133"/>
@@ -10413,7 +10413,7 @@
       <c r="E17" s="133"/>
       <c r="F17" s="134"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="132"/>
       <c r="B18" s="133"/>
       <c r="C18" s="133"/>
@@ -10421,7 +10421,7 @@
       <c r="E18" s="133"/>
       <c r="F18" s="134"/>
     </row>
-    <row r="19" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.15" thickBot="1">
       <c r="A19" s="135"/>
       <c r="B19" s="136"/>
       <c r="C19" s="136"/>
@@ -10429,8 +10429,8 @@
       <c r="E19" s="136"/>
       <c r="F19" s="137"/>
     </row>
-    <row r="20" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="13.15" thickBot="1"/>
+    <row r="21" spans="1:6">
       <c r="A21" s="93" t="s">
         <v>3</v>
       </c>
@@ -10440,7 +10440,7 @@
       <c r="E21" s="138"/>
       <c r="F21" s="139"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="94" t="s">
         <v>114</v>
       </c>
@@ -10450,7 +10450,7 @@
       <c r="E22" s="140"/>
       <c r="F22" s="141"/>
     </row>
-    <row r="23" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.15" thickBot="1">
       <c r="A23" s="95" t="s">
         <v>115</v>
       </c>
@@ -10514,18 +10514,18 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B2:J77"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.69921875" style="52"/>
+    <col min="1" max="1" width="8.75" style="52"/>
     <col min="2" max="2" width="25.5" style="52" customWidth="1"/>
-    <col min="3" max="3" width="8.69921875" style="52"/>
-    <col min="4" max="4" width="19.19921875" style="52" customWidth="1"/>
-    <col min="5" max="5" width="8.69921875" style="52"/>
-    <col min="6" max="6" width="21.69921875" style="52" customWidth="1"/>
-    <col min="7" max="16384" width="8.69921875" style="52"/>
+    <col min="3" max="3" width="8.75" style="52"/>
+    <col min="4" max="4" width="19.25" style="52" customWidth="1"/>
+    <col min="5" max="5" width="8.75" style="52"/>
+    <col min="6" max="6" width="21.75" style="52" customWidth="1"/>
+    <col min="7" max="16384" width="8.75" style="52"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" ht="15" thickBot="1">
       <c r="B2" s="66" t="s">
         <v>33</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10">
       <c r="B3" s="66" t="s">
         <v>118</v>
       </c>
@@ -10559,7 +10559,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10">
       <c r="B4" s="66" t="s">
         <v>120</v>
       </c>
@@ -10576,7 +10576,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10">
       <c r="B5" s="66" t="s">
         <v>124</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="B6" s="66" t="s">
         <v>128</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10">
       <c r="B7" s="66" t="s">
         <v>132</v>
       </c>
@@ -10618,7 +10618,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10">
       <c r="B8" s="66" t="s">
         <v>135</v>
       </c>
@@ -10635,7 +10635,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10">
       <c r="B9" s="66" t="s">
         <v>140</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10">
       <c r="B10" s="66" t="s">
         <v>144</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10">
       <c r="B11" s="66" t="s">
         <v>148</v>
       </c>
@@ -10683,7 +10683,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10">
       <c r="B12" s="66" t="s">
         <v>153</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10">
       <c r="B13" s="66" t="s">
         <v>157</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10">
       <c r="B14" s="66" t="s">
         <v>160</v>
       </c>
@@ -10720,7 +10720,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10">
       <c r="B15" s="66" t="s">
         <v>163</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10">
       <c r="B16" s="66" t="s">
         <v>166</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="27.6">
       <c r="B17" s="66" t="s">
         <v>169</v>
       </c>
@@ -10756,7 +10756,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8">
       <c r="B18" s="66" t="s">
         <v>172</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8">
       <c r="B19" s="66" t="s">
         <v>175</v>
       </c>
@@ -10780,7 +10780,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8">
       <c r="B20" s="66" t="s">
         <v>177</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8">
       <c r="B21" s="66" t="s">
         <v>180</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8">
       <c r="B22" s="66" t="s">
         <v>183</v>
       </c>
@@ -10816,7 +10816,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8">
       <c r="B23" s="66" t="s">
         <v>186</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8">
       <c r="B24" s="66" t="s">
         <v>189</v>
       </c>
@@ -10840,7 +10840,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8">
       <c r="B25" s="66" t="s">
         <v>192</v>
       </c>
@@ -10852,7 +10852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8">
       <c r="B26" s="66" t="s">
         <v>194</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8">
       <c r="B27" s="66" t="s">
         <v>197</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8">
       <c r="B28" s="66" t="s">
         <v>200</v>
       </c>
@@ -10887,7 +10887,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8">
       <c r="B29" s="66" t="s">
         <v>202</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8">
       <c r="B30" s="66" t="s">
         <v>205</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8">
       <c r="B31" s="66" t="s">
         <v>208</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:8">
       <c r="B32" s="66" t="s">
         <v>211</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8">
       <c r="B33" s="66" t="s">
         <v>214</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:8">
       <c r="B34" s="66" t="s">
         <v>217</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8">
       <c r="B35" s="66" t="s">
         <v>220</v>
       </c>
@@ -10964,7 +10964,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8">
       <c r="B36" s="66" t="s">
         <v>223</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:8">
       <c r="B37" s="66" t="s">
         <v>226</v>
       </c>
@@ -10986,7 +10986,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:8">
       <c r="B38" s="66" t="s">
         <v>229</v>
       </c>
@@ -10997,7 +10997,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8">
       <c r="B39" s="52" t="s">
         <v>231</v>
       </c>
@@ -11008,7 +11008,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:8">
       <c r="B40" s="66" t="s">
         <v>234</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:8">
       <c r="B41" s="66" t="s">
         <v>237</v>
       </c>
@@ -11028,7 +11028,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8">
       <c r="B42" s="66" t="s">
         <v>239</v>
       </c>
@@ -11036,7 +11036,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8">
       <c r="B43" s="52" t="s">
         <v>14</v>
       </c>
@@ -11044,174 +11044,174 @@
         <v>241</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:8" ht="27.6">
       <c r="B44" s="62"/>
       <c r="H44" s="108" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:8">
       <c r="H45" s="69" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:8">
       <c r="H46" s="112" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:8">
       <c r="B47" s="62"/>
       <c r="H47" s="111" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:8">
       <c r="H48" s="113" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="8:8">
       <c r="H49" s="99" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="50" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="8:8">
       <c r="H50" s="106" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="51" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="8:8">
       <c r="H51" s="110" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="52" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="8:8">
       <c r="H52" s="70" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="8:8">
       <c r="H53" s="70" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="8:8">
       <c r="H54" s="111" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="55" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="8:8">
       <c r="H55" s="70" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="56" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="8:8">
       <c r="H56" s="111" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="8:8">
       <c r="H57" s="70" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="58" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="8:8">
       <c r="H58" s="111" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="59" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="8:8">
       <c r="H59" s="69" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="60" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="8:8">
       <c r="H60" s="111" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="8:8">
       <c r="H61" s="69" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="62" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="8:8">
       <c r="H62" s="110" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="63" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="8:8">
       <c r="H63" s="108" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="64" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="8:8">
       <c r="H64" s="70" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="8:8">
       <c r="H65" s="111" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="8:8">
       <c r="H66" s="110" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="8:8">
       <c r="H67" s="108" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="8:8">
       <c r="H68" s="70" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="8:8">
       <c r="H69" s="70" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="8:8">
       <c r="H70" s="111" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="8:8">
       <c r="H71" s="114" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="8:8">
       <c r="H72" s="69" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="8:8">
       <c r="H73" s="109" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="8:8">
       <c r="H74" s="69" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="8:8">
       <c r="H75" s="109" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="8:8">
       <c r="H76" s="70" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="8:8">
       <c r="H77" s="71" t="s">
         <v>274</v>
       </c>
@@ -11232,18 +11232,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11385,38 +11385,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B75BA6D-7F73-4EF9-A999-8384A4D1B9F0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF9ADBEE-CE14-4AD5-B846-618264F5C11D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF9ADBEE-CE14-4AD5-B846-618264F5C11D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B75BA6D-7F73-4EF9-A999-8384A4D1B9F0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66237CC7-571C-424E-98D0-A6D854FCD4A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66237CC7-571C-424E-98D0-A6D854FCD4A2}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
